--- a/Train_A_Skill/Level1_Skill_Vertical_StraightArmPush_ChestToWallHandstandHold.xlsx
+++ b/Train_A_Skill/Level1_Skill_Vertical_StraightArmPush_ChestToWallHandstandHold.xlsx
@@ -93,7 +93,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +117,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFE599"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEAF6E1"/>
       </patternFill>
     </fill>
@@ -133,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -162,16 +167,19 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -539,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -618,41 +626,17 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>○  1</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>2 Arm Elevated Pike Hold + Scapula elevations</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>15 scap elevations · rest · 1 min hold</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>5–15 scap elevations · rest · 20–60s hold</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -730,17 +714,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Feet elevated handstand walkouts</t>
+          <t>2 Arm Elevated Pike Hold + Scapula elevations</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>10 reps, plank into piked handstand</t>
+          <t>15 scap elevations · rest · 1 min hold</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>6–10 reps</t>
+          <t>5–15 scap elevations · rest · 20–60s hold</t>
         </is>
       </c>
     </row>
@@ -752,17 +736,17 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Feet Elevated Scissor Switches</t>
+          <t>Feet elevated handstand walkouts</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>1 min hold, leg change every 2–3s</t>
+          <t>10 reps, plank into piked handstand</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>30–60s</t>
+          <t>6–10 reps</t>
         </is>
       </c>
     </row>
@@ -791,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -856,55 +840,79 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
+          <t>Feet Elevated Scissor Switches</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>1 min hold, leg change every 2–3s</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>30–60s</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
           <t>Back to wall HS kick ups</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>5 reps each side, 3–5s wall hold</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>3–5 reps each side</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>45 Degree Wall Handstand Hold</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>1 min hold, arms straight</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>30–60s</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="D9:F9"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -968,22 +976,22 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>TEST: Chest to Wall Handstand Hold</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>PASS: 1 minute hold</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>20–60s · 2 sets  ✦</t>
         </is>
